--- a/artfynd/A 24421-2025 artfynd.xlsx
+++ b/artfynd/A 24421-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668173</v>
+        <v>121668162</v>
       </c>
       <c r="B2" t="n">
-        <v>82417</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619912</v>
+        <v>619916</v>
       </c>
       <c r="R2" t="n">
-        <v>6935935</v>
+        <v>6935957</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121668171</v>
+        <v>121668164</v>
       </c>
       <c r="B3" t="n">
-        <v>98057</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spånbackrå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619895</v>
+        <v>619910</v>
       </c>
       <c r="R3" t="n">
-        <v>6935944</v>
+        <v>6935946</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668164</v>
+        <v>121668167</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619910</v>
+        <v>619944</v>
       </c>
       <c r="R4" t="n">
-        <v>6935946</v>
+        <v>6935986</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121668175</v>
+        <v>121668173</v>
       </c>
       <c r="B5" t="n">
-        <v>97094</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619906</v>
+        <v>619912</v>
       </c>
       <c r="R5" t="n">
-        <v>6935929</v>
+        <v>6935935</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121668162</v>
+        <v>121668163</v>
       </c>
       <c r="B6" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619916</v>
+        <v>619949</v>
       </c>
       <c r="R6" t="n">
-        <v>6935957</v>
+        <v>6935963</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121668163</v>
+        <v>121668171</v>
       </c>
       <c r="B7" t="n">
-        <v>78721</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,34 +1221,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spånbackrå, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619949</v>
+        <v>619895</v>
       </c>
       <c r="R7" t="n">
-        <v>6935963</v>
+        <v>6935944</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,6 +1318,113 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121668175</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spånbackrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>619906</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6935929</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24421-2025 artfynd.xlsx
+++ b/artfynd/A 24421-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668162</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668167</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668173</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668163</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668171</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,8 +1460,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668175</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>